--- a/tame_output/MOZAIC/data/universe_last2023-08-03.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-08-03.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>563.9973514152969</v>
+        <v>565.7278776124394</v>
       </c>
       <c r="E2" t="n">
-        <v>15553.34194841573</v>
+        <v>15134.86222295772</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5870206492308232</v>
+        <v>0.5912266864484743</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4940426033897953</v>
+        <v>0.4940157795035092</v>
       </c>
       <c r="H2" t="n">
-        <v>1.188198437145043</v>
+        <v>1.196776926928656</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>220.0767931129104</v>
+        <v>220.1490251099118</v>
       </c>
       <c r="E3" t="n">
-        <v>5532.828148676906</v>
+        <v>5554.411022104585</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2257669708547387</v>
+        <v>0.224848022109003</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5919345683530691</v>
+        <v>0.5919399662560137</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3814052818082358</v>
+        <v>0.3798493680552672</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.890731408244771</v>
+        <v>0.8907459392943289</v>
       </c>
       <c r="N3" t="n">
-        <v>1.067225190783578</v>
+        <v>1.067310282636065</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>36.8328424171885</v>
+        <v>36.77469927139693</v>
       </c>
       <c r="E4" t="n">
-        <v>551.8692010110531</v>
+        <v>558.750243068846</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3333247789775368</v>
+        <v>-0.3351632378159528</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5572082492950186</v>
+        <v>0.5572302830316984</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.5982050326772086</v>
+        <v>-0.6014806589341212</v>
       </c>
       <c r="I4" t="n">
         <v>0.3496897913141569</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.7371149500427141</v>
+        <v>0.7371331416543209</v>
       </c>
       <c r="N4" t="n">
-        <v>0.831358526621693</v>
+        <v>0.8314570631101965</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>35.33833064696901</v>
+        <v>34.97759072354614</v>
       </c>
       <c r="E5" t="n">
-        <v>1187.915448837933</v>
+        <v>1351.093872453938</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6292872483572198</v>
+        <v>0.6062174504463407</v>
       </c>
       <c r="G5" t="n">
-        <v>1.097650082592345</v>
+        <v>1.098000094374298</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5733040595879317</v>
+        <v>0.5521105631523623</v>
       </c>
       <c r="I5" t="n">
         <v>0.3422195892575038</v>
@@ -706,45 +706,45 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.4747232431298053</v>
+        <v>0.4745920168053147</v>
       </c>
       <c r="N5" t="n">
-        <v>1.054726866579174</v>
+        <v>1.054828814912019</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>DOGE</t>
+          <t>ADA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DOGE</t>
+          <t>ADA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dogecoin</t>
+          <t>Cardano</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.40664043169266</v>
+        <v>10.32531321839778</v>
       </c>
       <c r="E6" t="n">
-        <v>374.3050105015577</v>
+        <v>263.577854464495</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.5079936830264131</v>
+        <v>-0.3443193890917106</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8091780922943985</v>
+        <v>0.70886118862766</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.6277897138638706</v>
+        <v>-0.4857359869825931</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5751178664414889</v>
+        <v>0.4277673545966229</v>
       </c>
       <c r="J6" t="n">
         <v>276</v>
@@ -760,45 +760,45 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.667160945720662</v>
+        <v>0.7507831756017898</v>
       </c>
       <c r="N6" t="n">
-        <v>1.092723618585649</v>
+        <v>1.077295658032627</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>ADA</t>
+          <t>DOGE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ADA</t>
+          <t>DOGE</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Cardano</t>
+          <t>Dogecoin</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.33251255619062</v>
+        <v>10.28355747526329</v>
       </c>
       <c r="E7" t="n">
-        <v>250.6621841632803</v>
+        <v>409.4358167245775</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.342258947868137</v>
+        <v>-0.5165689578064516</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7088018732283516</v>
+        <v>0.8093022417761854</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4828696999759098</v>
+        <v>-0.6382892955698869</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4277673545966229</v>
+        <v>0.5751178664414889</v>
       </c>
       <c r="J7" t="n">
         <v>276</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.7508632495501265</v>
+        <v>0.6672762986962979</v>
       </c>
       <c r="N7" t="n">
-        <v>1.077261908523191</v>
+        <v>1.093139585463774</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.159675706897632</v>
+        <v>9.180566098991754</v>
       </c>
       <c r="E8" t="n">
-        <v>375.1911751568943</v>
+        <v>389.0052076172121</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3790198540105074</v>
+        <v>-0.3801044627037836</v>
       </c>
       <c r="G8" t="n">
-        <v>1.161019920886645</v>
+        <v>1.16104955864605</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3264542211481249</v>
+        <v>-0.3273800501220979</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7376468002669697</v>
+        <v>0.7375907018736494</v>
       </c>
       <c r="N8" t="n">
-        <v>1.733499548039046</v>
+        <v>1.733506083009131</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>6.850494731576987</v>
+        <v>6.84851975413517</v>
       </c>
       <c r="E9" t="n">
-        <v>195.0467711467486</v>
+        <v>193.1347395850655</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2868766885748166</v>
+        <v>0.2862096882207674</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4809123388375333</v>
+        <v>0.48091054750521</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5965259474694665</v>
+        <v>0.5951412163977684</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6740894545840108</v>
+        <v>0.6741579586425801</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6561740505078267</v>
+        <v>0.656273921698679</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.336492518576206</v>
+        <v>6.319422201979811</v>
       </c>
       <c r="E10" t="n">
-        <v>870.7926422925271</v>
+        <v>859.7473798506409</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8159286773974579</v>
+        <v>0.8031494693967147</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8178757372619049</v>
+        <v>0.8180314915170013</v>
       </c>
       <c r="H10" t="n">
-        <v>0.9976193695744474</v>
+        <v>0.9818075193013798</v>
       </c>
       <c r="I10" t="n">
         <v>0.3268819295856837</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.6644276974531279</v>
+        <v>0.6643040006090947</v>
       </c>
       <c r="N10" t="n">
-        <v>1.099944193442268</v>
+        <v>1.100008572570521</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.269324237848083</v>
+        <v>6.279736279634808</v>
       </c>
       <c r="E11" t="n">
-        <v>273.5329941796925</v>
+        <v>278.9679345411315</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.3217153818356601</v>
+        <v>-0.3211821914763693</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9498339052260285</v>
+        <v>0.9498252153177699</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.3387069887330487</v>
+        <v>-0.3381487312577987</v>
       </c>
       <c r="I11" t="n">
         <v>0.6126386245816655</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.7138839604473795</v>
+        <v>0.7138612531891936</v>
       </c>
       <c r="N11" t="n">
-        <v>1.372495378693011</v>
+        <v>1.372513686099013</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.129110784721044</v>
+        <v>6.276252833865331</v>
       </c>
       <c r="E12" t="n">
-        <v>106.7645922758017</v>
+        <v>106.8667902394329</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.3091534268553099</v>
+        <v>-0.3064139840894491</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6528277664357824</v>
+        <v>0.6527732868275221</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4735604745232919</v>
+        <v>-0.4694033752187087</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.789472103557318</v>
+        <v>0.7894455825236636</v>
       </c>
       <c r="N12" t="n">
-        <v>1.043208230408512</v>
+        <v>1.043142768017148</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.415982960941383</v>
+        <v>4.424493721534597</v>
       </c>
       <c r="E13" t="n">
-        <v>290.716588958635</v>
+        <v>284.5723585264943</v>
       </c>
       <c r="F13" t="n">
-        <v>1.460743828028271</v>
+        <v>1.457879582790506</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8574154623423382</v>
+        <v>0.8574316450740687</v>
       </c>
       <c r="H13" t="n">
-        <v>1.703659301918494</v>
+        <v>1.700286653946121</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.6016336826030539</v>
+        <v>0.6015938494218864</v>
       </c>
       <c r="N13" t="n">
-        <v>1.044140765574461</v>
+        <v>1.044148032062173</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.303395115273701</v>
+        <v>4.31906329707967</v>
       </c>
       <c r="E14" t="n">
-        <v>116.4882051399579</v>
+        <v>117.6576247327352</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4397874924291435</v>
+        <v>-0.4374040694388966</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8419976609641456</v>
+        <v>0.8419651436939597</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.5223143873411197</v>
+        <v>-0.5195037736596442</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.7602706924149849</v>
+        <v>0.7602492339382411</v>
       </c>
       <c r="N14" t="n">
-        <v>1.295730652216524</v>
+        <v>1.295714392239341</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>3.931336300701285</v>
+        <v>3.904113721618729</v>
       </c>
       <c r="E15" t="n">
-        <v>252.8614939015463</v>
+        <v>256.5061762171175</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.08970319578993458</v>
+        <v>-0.1005445880602791</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7881782490063233</v>
+        <v>0.7883208185693219</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.1138107983860576</v>
+        <v>-0.1275427284068835</v>
       </c>
       <c r="I15" t="n">
         <v>0.4268646717284502</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.7138007699829085</v>
+        <v>0.7137995072247084</v>
       </c>
       <c r="N15" t="n">
-        <v>1.138772723575432</v>
+        <v>1.139038539204725</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3.900542100857166</v>
+        <v>3.882185104281269</v>
       </c>
       <c r="E16" t="n">
-        <v>131.3317330217613</v>
+        <v>135.9338838663799</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3929582863712813</v>
+        <v>0.3800907578894748</v>
       </c>
       <c r="G16" t="n">
-        <v>0.955022690356893</v>
+        <v>0.9551405221178666</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4114648692005761</v>
+        <v>0.3979422389563017</v>
       </c>
       <c r="I16" t="n">
         <v>0.3858131487889274</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.5154271306952531</v>
+        <v>0.5154208161754918</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9963606410905779</v>
+        <v>0.9965254712451533</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.534697137267177</v>
+        <v>3.538164404490381</v>
       </c>
       <c r="E17" t="n">
-        <v>118.7356463040529</v>
+        <v>106.0597286784117</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1529474078572551</v>
+        <v>-0.1545892686537061</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7541635072251468</v>
+        <v>0.7541740409977181</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2028040423488622</v>
+        <v>-0.2049782414271322</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7204356676238755</v>
+        <v>0.7204616887378489</v>
       </c>
       <c r="N17" t="n">
-        <v>1.099755944320114</v>
+        <v>1.099870744463951</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.001254668008957</v>
+        <v>2.996538909773903</v>
       </c>
       <c r="E18" t="n">
-        <v>76.1246591621959</v>
+        <v>78.10207199088413</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4847997165858474</v>
+        <v>-0.4869199620882767</v>
       </c>
       <c r="G18" t="n">
-        <v>0.738916343450302</v>
+        <v>0.7389473221659744</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6560955389376282</v>
+        <v>-0.6589373118790598</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.764990107183378</v>
+        <v>0.7650155705189843</v>
       </c>
       <c r="N18" t="n">
-        <v>1.144159813135808</v>
+        <v>1.144307997243361</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.930608339453306</v>
+        <v>2.942477408707909</v>
       </c>
       <c r="E19" t="n">
-        <v>95.89704248769418</v>
+        <v>94.44735447088772</v>
       </c>
       <c r="F19" t="n">
-        <v>0.09475783522614334</v>
+        <v>0.1010884068712883</v>
       </c>
       <c r="G19" t="n">
-        <v>0.476512812664542</v>
+        <v>0.4765396746482952</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1988568464639616</v>
+        <v>0.2121300958747988</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7157323172658989</v>
+        <v>0.7156322345968067</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6903364553485564</v>
+        <v>0.6903163145625237</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.55200907563274</v>
+        <v>2.551299621424187</v>
       </c>
       <c r="E20" t="n">
-        <v>115.5284935836487</v>
+        <v>116.6674897466149</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3282252243898399</v>
+        <v>-0.3287201090654268</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7708870124600803</v>
+        <v>0.7708937610229841</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4257760464045135</v>
+        <v>-0.4264142813002038</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7321590741368166</v>
+        <v>0.7321528091196562</v>
       </c>
       <c r="N20" t="n">
-        <v>1.142435728081436</v>
+        <v>1.142497985050263</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-08-03.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-08-03.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>565.7278776124394</v>
+        <v>566.2993945560364</v>
       </c>
       <c r="E2" t="n">
-        <v>15134.86222295772</v>
+        <v>14768.88117641952</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5912266864484743</v>
+        <v>0.5939803960948311</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4940157795035092</v>
+        <v>0.4940039112798107</v>
       </c>
       <c r="H2" t="n">
-        <v>1.196776926928656</v>
+        <v>1.202379945851061</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>220.1490251099118</v>
+        <v>220.4559460573509</v>
       </c>
       <c r="E3" t="n">
-        <v>5554.411022104585</v>
+        <v>5495.780331938448</v>
       </c>
       <c r="F3" t="n">
-        <v>0.224848022109003</v>
+        <v>0.2279147847544087</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5919399662560137</v>
+        <v>0.5919247001398636</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3798493680552672</v>
+        <v>0.3850401659206916</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8907459392943289</v>
+        <v>0.8907399527452663</v>
       </c>
       <c r="N3" t="n">
-        <v>1.067310282636065</v>
+        <v>1.067301224529568</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>36.77469927139693</v>
+        <v>36.93589791202198</v>
       </c>
       <c r="E4" t="n">
-        <v>558.750243068846</v>
+        <v>561.0379889260184</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3351632378159528</v>
+        <v>-0.3311169956345936</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5572302830316984</v>
+        <v>0.5571951414337434</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.6014806589341212</v>
+        <v>-0.5942567890713869</v>
       </c>
       <c r="I4" t="n">
         <v>0.3496897913141569</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.7371331416543209</v>
+        <v>0.7371024396283112</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8314570631101965</v>
+        <v>0.8313899722693132</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>34.97759072354614</v>
+        <v>35.01643141911512</v>
       </c>
       <c r="E5" t="n">
-        <v>1351.093872453938</v>
+        <v>1401.793530905705</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6062174504463407</v>
+        <v>0.6100568414686545</v>
       </c>
       <c r="G5" t="n">
-        <v>1.098000094374298</v>
+        <v>1.097932652233075</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5521105631523623</v>
+        <v>0.5556414049876969</v>
       </c>
       <c r="I5" t="n">
         <v>0.3422195892575038</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.4745920168053147</v>
+        <v>0.4745163526960088</v>
       </c>
       <c r="N5" t="n">
-        <v>1.054828814912019</v>
+        <v>1.05462119984795</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.32531321839778</v>
+        <v>10.34047737561395</v>
       </c>
       <c r="E6" t="n">
-        <v>263.577854464495</v>
+        <v>272.0185364315715</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3443193890917106</v>
+        <v>-0.3401969315922435</v>
       </c>
       <c r="G6" t="n">
-        <v>0.70886118862766</v>
+        <v>0.7087526195033567</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4857359869825931</v>
+        <v>-0.4799938966442611</v>
       </c>
       <c r="I6" t="n">
         <v>0.4277673545966229</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.7507831756017898</v>
+        <v>0.7507948820231949</v>
       </c>
       <c r="N6" t="n">
-        <v>1.077295658032627</v>
+        <v>1.077173332423776</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.28355747526329</v>
+        <v>10.31891189309393</v>
       </c>
       <c r="E7" t="n">
-        <v>409.4358167245775</v>
+        <v>420.2309288211061</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5165689578064516</v>
+        <v>-0.5137729126238242</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8093022417761854</v>
+        <v>0.8092308069532133</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.6382892955698869</v>
+        <v>-0.634890451783713</v>
       </c>
       <c r="I7" t="n">
         <v>0.5751178664414889</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.6672762986962979</v>
+        <v>0.6672590099986597</v>
       </c>
       <c r="N7" t="n">
-        <v>1.093139585463774</v>
+        <v>1.093041036272632</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.180566098991754</v>
+        <v>9.199142373964184</v>
       </c>
       <c r="E8" t="n">
-        <v>389.0052076172121</v>
+        <v>394.0343960453604</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3801044627037836</v>
+        <v>-0.3764873039901582</v>
       </c>
       <c r="G8" t="n">
-        <v>1.16104955864605</v>
+        <v>1.16095810060783</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3273800501220979</v>
+        <v>-0.3242901736014805</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7375907018736494</v>
+        <v>0.737576756323989</v>
       </c>
       <c r="N8" t="n">
-        <v>1.733506083009131</v>
+        <v>1.733378401511003</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>6.84851975413517</v>
+        <v>6.878837740947329</v>
       </c>
       <c r="E9" t="n">
-        <v>193.1347395850655</v>
+        <v>195.5585922580549</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2862096882207674</v>
+        <v>0.2935513253506925</v>
       </c>
       <c r="G9" t="n">
-        <v>0.48091054750521</v>
+        <v>0.4809532995892873</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5951412163977684</v>
+        <v>0.6103530750311356</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6741579586425801</v>
+        <v>0.6740585896926271</v>
       </c>
       <c r="N9" t="n">
-        <v>0.656273921698679</v>
+        <v>0.6562512875440464</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.319422201979811</v>
+        <v>6.332026145175248</v>
       </c>
       <c r="E10" t="n">
-        <v>859.7473798506409</v>
+        <v>860.1279982883882</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8031494693967147</v>
+        <v>0.811203363481295</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8180314915170013</v>
+        <v>0.8179281725049096</v>
       </c>
       <c r="H10" t="n">
-        <v>0.9818075193013798</v>
+        <v>0.9917782401319912</v>
       </c>
       <c r="I10" t="n">
         <v>0.3268819295856837</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.6643040006090947</v>
+        <v>0.6642846442462622</v>
       </c>
       <c r="N10" t="n">
-        <v>1.100008572570521</v>
+        <v>1.099864014606284</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.279736279634808</v>
+        <v>6.290932972016829</v>
       </c>
       <c r="E11" t="n">
-        <v>278.9679345411315</v>
+        <v>280.4053750843103</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.3211821914763693</v>
+        <v>-0.317980905837684</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9498252153177699</v>
+        <v>0.9497830416000854</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.3381487312577987</v>
+        <v>-0.3347932021422348</v>
       </c>
       <c r="I11" t="n">
         <v>0.6126386245816655</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.7138612531891936</v>
+        <v>0.7138447413670028</v>
       </c>
       <c r="N11" t="n">
-        <v>1.372513686099013</v>
+        <v>1.372453970919576</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.276252833865331</v>
+        <v>6.150486703117137</v>
       </c>
       <c r="E12" t="n">
-        <v>106.8667902394329</v>
+        <v>105.9150317578897</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.3064139840894491</v>
+        <v>-0.3056830197910193</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6527732868275221</v>
+        <v>0.6527617226585521</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4694033752187087</v>
+        <v>-0.468291888418397</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7894455825236636</v>
+        <v>0.7894288691060545</v>
       </c>
       <c r="N12" t="n">
-        <v>1.043142768017148</v>
+        <v>1.043127264274195</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.424493721534597</v>
+        <v>4.453477573720424</v>
       </c>
       <c r="E13" t="n">
-        <v>284.5723585264943</v>
+        <v>286.4910706087626</v>
       </c>
       <c r="F13" t="n">
-        <v>1.457879582790506</v>
+        <v>1.49086740502174</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8574316450740687</v>
+        <v>0.8573155315620627</v>
       </c>
       <c r="H13" t="n">
-        <v>1.700286653946121</v>
+        <v>1.738994979252645</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.6015938494218864</v>
+        <v>0.601552734095529</v>
       </c>
       <c r="N13" t="n">
-        <v>1.044148032062173</v>
+        <v>1.043960361887923</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.31906329707967</v>
+        <v>4.330475804110011</v>
       </c>
       <c r="E14" t="n">
-        <v>117.6576247327352</v>
+        <v>118.8960775064924</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4374040694388966</v>
+        <v>-0.4350181818141244</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8419651436939597</v>
+        <v>0.8419483629870895</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.5195037736596442</v>
+        <v>-0.5166803582475699</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.7602492339382411</v>
+        <v>0.7602343161481868</v>
       </c>
       <c r="N14" t="n">
-        <v>1.295714392239341</v>
+        <v>1.295694271548037</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>3.904113721618729</v>
+        <v>3.927463754344909</v>
       </c>
       <c r="E15" t="n">
-        <v>256.5061762171175</v>
+        <v>255.8007193671383</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.1005445880602791</v>
+        <v>-0.09085454067606535</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7883208185693219</v>
+        <v>0.7881870472761167</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.1275427284068835</v>
+        <v>-0.1152702787873109</v>
       </c>
       <c r="I15" t="n">
         <v>0.4268646717284502</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.7137995072247084</v>
+        <v>0.7138011655995546</v>
       </c>
       <c r="N15" t="n">
-        <v>1.139038539204725</v>
+        <v>1.1388752603165</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3.882185104281269</v>
+        <v>3.87434706160419</v>
       </c>
       <c r="E16" t="n">
-        <v>135.9338838663799</v>
+        <v>136.1037915027093</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3800907578894748</v>
+        <v>0.3788056080582147</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9551405221178666</v>
+        <v>0.9551559265714221</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3979422389563017</v>
+        <v>0.3965903341226762</v>
       </c>
       <c r="I16" t="n">
         <v>0.3858131487889274</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.5154208161754918</v>
+        <v>0.5153728961340304</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9965254712451533</v>
+        <v>0.9964728312806278</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.538164404490381</v>
+        <v>3.577214394136115</v>
       </c>
       <c r="E17" t="n">
-        <v>106.0597286784117</v>
+        <v>105.6154829385069</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1545892686537061</v>
+        <v>-0.1403340725736436</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7541740409977181</v>
+        <v>0.754205479819837</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2049782414271322</v>
+        <v>-0.1860687522545796</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7204616887378489</v>
+        <v>0.7203027931646737</v>
       </c>
       <c r="N17" t="n">
-        <v>1.099870744463951</v>
+        <v>1.099700430158383</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>2.996538909773903</v>
+        <v>3.005549069994378</v>
       </c>
       <c r="E18" t="n">
-        <v>78.10207199088413</v>
+        <v>78.82644909671987</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4869199620882767</v>
+        <v>-0.4835422695304242</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7389473221659744</v>
+        <v>0.738905976628471</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6589373118790598</v>
+        <v>-0.6544029752428893</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7650155705189843</v>
+        <v>0.7649939028238795</v>
       </c>
       <c r="N18" t="n">
-        <v>1.144307997243361</v>
+        <v>1.144239051501626</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.942477408707909</v>
+        <v>2.949248493586124</v>
       </c>
       <c r="E19" t="n">
-        <v>94.44735447088772</v>
+        <v>92.71095484044355</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1010884068712883</v>
+        <v>0.1038042311447209</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4765396746482952</v>
+        <v>0.4765672036104967</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2121300958747988</v>
+        <v>0.2178165647117446</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7156322345968067</v>
+        <v>0.7156111416733519</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6903163145625237</v>
+        <v>0.6903524301584253</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.551299621424187</v>
+        <v>2.564934417140738</v>
       </c>
       <c r="E20" t="n">
-        <v>116.6674897466149</v>
+        <v>117.4231948594331</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3287201090654268</v>
+        <v>-0.3232714930083709</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7708937610229841</v>
+        <v>0.7708479943066152</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4264142813002038</v>
+        <v>-0.4193712578822451</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7321528091196562</v>
+        <v>0.7321222194655107</v>
       </c>
       <c r="N20" t="n">
-        <v>1.142497985050263</v>
+        <v>1.142409870804925</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-08-03.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-08-03.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>566.2993945560364</v>
+        <v>566.3814646025372</v>
       </c>
       <c r="E2" t="n">
-        <v>14768.88117641952</v>
+        <v>14484.98357285023</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5939803960948311</v>
+        <v>0.5952828299149382</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4940039112798107</v>
+        <v>0.4939998654591828</v>
       </c>
       <c r="H2" t="n">
-        <v>1.202379945851061</v>
+        <v>1.20502629967644</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>220.4559460573509</v>
+        <v>220.516994696052</v>
       </c>
       <c r="E3" t="n">
-        <v>5495.780331938448</v>
+        <v>5429.705319388421</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2279147847544087</v>
+        <v>0.2287723985389249</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5919247001398636</v>
+        <v>0.5919218343308178</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3850401659206916</v>
+        <v>0.3864908933416146</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8907399527452663</v>
+        <v>0.8907389306198424</v>
       </c>
       <c r="N3" t="n">
-        <v>1.067301224529568</v>
+        <v>1.067303573518751</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>36.93589791202198</v>
+        <v>37.02097932307754</v>
       </c>
       <c r="E4" t="n">
-        <v>561.0379889260184</v>
+        <v>562.0274528507837</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3311169956345936</v>
+        <v>-0.3285390010123694</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5571951414337434</v>
+        <v>0.5571982329649345</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.5942567890713869</v>
+        <v>-0.5896267819518461</v>
       </c>
       <c r="I4" t="n">
         <v>0.3496897913141569</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.7371024396283112</v>
+        <v>0.737071494466998</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8313899722693132</v>
+        <v>0.8313664901590319</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>35.01643141911512</v>
+        <v>35.00336204942854</v>
       </c>
       <c r="E5" t="n">
-        <v>1401.793530905705</v>
+        <v>1439.568410190007</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6100568414686545</v>
+        <v>0.6106969572156886</v>
       </c>
       <c r="G5" t="n">
-        <v>1.097932652233075</v>
+        <v>1.097921765934866</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5556414049876969</v>
+        <v>0.5562299392941609</v>
       </c>
       <c r="I5" t="n">
         <v>0.3422195892575038</v>
@@ -706,45 +706,45 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.4745163526960088</v>
+        <v>0.4744766251876887</v>
       </c>
       <c r="N5" t="n">
-        <v>1.05462119984795</v>
+        <v>1.054531085219345</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>ADA</t>
+          <t>DOGE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ADA</t>
+          <t>DOGE</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Cardano</t>
+          <t>Dogecoin</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.34047737561395</v>
+        <v>10.32501633913364</v>
       </c>
       <c r="E6" t="n">
-        <v>272.0185364315715</v>
+        <v>426.9508247828504</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3401969315922435</v>
+        <v>-0.5129858170352183</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7087526195033567</v>
+        <v>0.8092161134186174</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4799938966442611</v>
+        <v>-0.6339293157028923</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4277673545966229</v>
+        <v>0.5751178664414889</v>
       </c>
       <c r="J6" t="n">
         <v>276</v>
@@ -760,45 +760,45 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.7507948820231949</v>
+        <v>0.6672516296121749</v>
       </c>
       <c r="N6" t="n">
-        <v>1.077173332423776</v>
+        <v>1.093018051503127</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>DOGE</t>
+          <t>ADA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DOGE</t>
+          <t>ADA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Dogecoin</t>
+          <t>Cardano</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.31891189309393</v>
+        <v>10.32445983209593</v>
       </c>
       <c r="E7" t="n">
-        <v>420.2309288211061</v>
+        <v>302.3129309458538</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5137729126238242</v>
+        <v>-0.3434365358788751</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8092308069532133</v>
+        <v>0.7088345358526849</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.634890451783713</v>
+        <v>-0.4845087513487782</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5751178664414889</v>
+        <v>0.4277673545966229</v>
       </c>
       <c r="J7" t="n">
         <v>276</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.6672590099986597</v>
+        <v>0.7507204192629132</v>
       </c>
       <c r="N7" t="n">
-        <v>1.093041036272632</v>
+        <v>1.077199807430572</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.199142373964184</v>
+        <v>9.194903905479146</v>
       </c>
       <c r="E8" t="n">
-        <v>394.0343960453604</v>
+        <v>399.5656543554236</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3764873039901582</v>
+        <v>-0.376849250689968</v>
       </c>
       <c r="G8" t="n">
-        <v>1.16095810060783</v>
+        <v>1.16096630336133</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3242901736014805</v>
+        <v>-0.3245996456562791</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.737576756323989</v>
+        <v>0.7375563047920947</v>
       </c>
       <c r="N8" t="n">
-        <v>1.733378401511003</v>
+        <v>1.733356781179268</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>6.878837740947329</v>
+        <v>6.885026153787469</v>
       </c>
       <c r="E9" t="n">
-        <v>195.5585922580549</v>
+        <v>196.5895015239688</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2935513253506925</v>
+        <v>0.2957780739218845</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4809532995892873</v>
+        <v>0.4809762640610218</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6103530750311356</v>
+        <v>0.6149535767618647</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6740585896926271</v>
+        <v>0.6740359581205013</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6562512875440464</v>
+        <v>0.6562659620934189</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.332026145175248</v>
+        <v>6.331060157436462</v>
       </c>
       <c r="E10" t="n">
-        <v>860.1279982883882</v>
+        <v>850.9838353654575</v>
       </c>
       <c r="F10" t="n">
-        <v>0.811203363481295</v>
+        <v>0.8106476416212571</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8179281725049096</v>
+        <v>0.8179347365166608</v>
       </c>
       <c r="H10" t="n">
-        <v>0.9917782401319912</v>
+        <v>0.9910908602238399</v>
       </c>
       <c r="I10" t="n">
         <v>0.3268819295856837</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.6642846442462622</v>
+        <v>0.664250696467938</v>
       </c>
       <c r="N10" t="n">
-        <v>1.099864014606284</v>
+        <v>1.099825640420954</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.290932972016829</v>
+        <v>6.281331062509398</v>
       </c>
       <c r="E11" t="n">
-        <v>280.4053750843103</v>
+        <v>282.5145961306632</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.317980905837684</v>
+        <v>-0.3206488989780534</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9497830416000854</v>
+        <v>0.9498169999488338</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.3347932021422348</v>
+        <v>-0.3375901873680157</v>
       </c>
       <c r="I11" t="n">
         <v>0.6126386245816655</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.7138447413670028</v>
+        <v>0.7138309257285782</v>
       </c>
       <c r="N11" t="n">
-        <v>1.372453970919576</v>
+        <v>1.372487718627198</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.150486703117137</v>
+        <v>6.142129050896719</v>
       </c>
       <c r="E12" t="n">
-        <v>105.9150317578897</v>
+        <v>105.752247033673</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.3056830197910193</v>
+        <v>-0.3062312606164028</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6527617226585521</v>
+        <v>0.6527702787867765</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.468291888418397</v>
+        <v>-0.4691256182581674</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7894288691060545</v>
+        <v>0.7894129105632541</v>
       </c>
       <c r="N12" t="n">
-        <v>1.043127264274195</v>
+        <v>1.043128392812961</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.453477573720424</v>
+        <v>4.439764031229545</v>
       </c>
       <c r="E13" t="n">
-        <v>286.4910706087626</v>
+        <v>279.13691459733</v>
       </c>
       <c r="F13" t="n">
-        <v>1.49086740502174</v>
+        <v>1.477946358817843</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8573155315620627</v>
+        <v>0.8573427081506356</v>
       </c>
       <c r="H13" t="n">
-        <v>1.738994979252645</v>
+        <v>1.723868815547407</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.601552734095529</v>
+        <v>0.6015599930834816</v>
       </c>
       <c r="N13" t="n">
-        <v>1.043960361887923</v>
+        <v>1.044014603335724</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.330475804110011</v>
+        <v>4.326480718840996</v>
       </c>
       <c r="E14" t="n">
-        <v>118.8960775064924</v>
+        <v>121.3738490206422</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4350181818141244</v>
+        <v>-0.4356148844874015</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8419483629870895</v>
+        <v>0.8419510827944597</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.5166803582475699</v>
+        <v>-0.5173874033650306</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.7602343161481868</v>
+        <v>0.7602400277477941</v>
       </c>
       <c r="N14" t="n">
-        <v>1.295694271548037</v>
+        <v>1.295718803386664</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>3.927463754344909</v>
+        <v>3.909673596693526</v>
       </c>
       <c r="E15" t="n">
-        <v>255.8007193671383</v>
+        <v>254.4551639809041</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.09085454067606535</v>
+        <v>-0.09923216808568924</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7881870472761167</v>
+        <v>0.788296434880192</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.1152702787873109</v>
+        <v>-0.1258817922990745</v>
       </c>
       <c r="I15" t="n">
         <v>0.4268646717284502</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.7138011655995546</v>
+        <v>0.7137459704988954</v>
       </c>
       <c r="N15" t="n">
-        <v>1.1388752603165</v>
+        <v>1.138954569211054</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3.87434706160419</v>
+        <v>3.817484707894844</v>
       </c>
       <c r="E16" t="n">
-        <v>136.1037915027093</v>
+        <v>142.9817512884928</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3788056080582147</v>
+        <v>0.3518851327917016</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9551559265714221</v>
+        <v>0.9556314260734823</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3965903341226762</v>
+        <v>0.3682226465045571</v>
       </c>
       <c r="I16" t="n">
         <v>0.3858131487889274</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.5153728961340304</v>
+        <v>0.5151800128695355</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9964728312806278</v>
+        <v>0.9966039361679699</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.577214394136115</v>
+        <v>3.582969171978111</v>
       </c>
       <c r="E17" t="n">
-        <v>105.6154829385069</v>
+        <v>105.8768899009572</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1403340725736436</v>
+        <v>-0.1407003154809585</v>
       </c>
       <c r="G17" t="n">
-        <v>0.754205479819837</v>
+        <v>0.7542012076258751</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1860687522545796</v>
+        <v>-0.1865554099599818</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7203027931646737</v>
+        <v>0.7203320273780864</v>
       </c>
       <c r="N17" t="n">
-        <v>1.099700430158383</v>
+        <v>1.099747839880811</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.005549069994378</v>
+        <v>3.011871129574472</v>
       </c>
       <c r="E18" t="n">
-        <v>78.82644909671987</v>
+        <v>78.71776636331518</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4835422695304242</v>
+        <v>-0.4826773413257583</v>
       </c>
       <c r="G18" t="n">
-        <v>0.738905976628471</v>
+        <v>0.7389022992006277</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6544029752428893</v>
+        <v>-0.6532356738474584</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7649939028238795</v>
+        <v>0.7649891379599251</v>
       </c>
       <c r="N18" t="n">
-        <v>1.144239051501626</v>
+        <v>1.14423560090787</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.949248493586124</v>
+        <v>2.935690891762875</v>
       </c>
       <c r="E19" t="n">
-        <v>92.71095484044355</v>
+        <v>90.56410696350591</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1038042311447209</v>
+        <v>0.09746984743237097</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4765672036104967</v>
+        <v>0.4765179177580218</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2178165647117446</v>
+        <v>0.2045460281765662</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7156111416733519</v>
+        <v>0.7157652581710697</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6903524301584253</v>
+        <v>0.6904353508480718</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.564934417140738</v>
+        <v>2.56416745571162</v>
       </c>
       <c r="E20" t="n">
-        <v>117.4231948594331</v>
+        <v>118.3091051128497</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3232714930083709</v>
+        <v>-0.3242629489733968</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7708479943066152</v>
+        <v>0.7708516570061898</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4193712578822451</v>
+        <v>-0.4206554478104897</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7321222194655107</v>
+        <v>0.7321300094934824</v>
       </c>
       <c r="N20" t="n">
-        <v>1.142409870804925</v>
+        <v>1.142436811065567</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-08-03.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-08-03.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>566.3814646025372</v>
+        <v>568.1851174145963</v>
       </c>
       <c r="E2" t="n">
-        <v>14484.98357285023</v>
+        <v>14207.67797221199</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5952828299149382</v>
+        <v>0.600348947410442</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4939998654591828</v>
+        <v>0.4939936888562471</v>
       </c>
       <c r="H2" t="n">
-        <v>1.20502629967644</v>
+        <v>1.215296796200861</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>220.516994696052</v>
+        <v>221.0860945667272</v>
       </c>
       <c r="E3" t="n">
-        <v>5429.705319388421</v>
+        <v>5112.198452073358</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2287723985389249</v>
+        <v>0.2315938276526264</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5919218343308178</v>
+        <v>0.5919167287287056</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3864908933416146</v>
+        <v>0.3912608250657725</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8907389306198424</v>
+        <v>0.8907359084898543</v>
       </c>
       <c r="N3" t="n">
-        <v>1.067303573518751</v>
+        <v>1.067304091141809</v>
       </c>
     </row>
     <row r="4">
@@ -621,10 +621,10 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>37.02097932307754</v>
+        <v>37.05499449884983</v>
       </c>
       <c r="E4" t="n">
-        <v>562.0274528507837</v>
+        <v>551.5576258786034</v>
       </c>
       <c r="F4" t="n">
         <v>-0.3285390010123694</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.737071494466998</v>
+        <v>0.7371024041599193</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8313664901590319</v>
+        <v>0.8314117495368041</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>35.00336204942854</v>
+        <v>35.27363958126086</v>
       </c>
       <c r="E5" t="n">
-        <v>1439.568410190007</v>
+        <v>1394.773667283345</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6106969572156886</v>
+        <v>0.6222296365726347</v>
       </c>
       <c r="G5" t="n">
-        <v>1.097921765934866</v>
+        <v>1.097743115030809</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5562299392941609</v>
+        <v>0.5668262711492128</v>
       </c>
       <c r="I5" t="n">
         <v>0.3422195892575038</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.4744766251876887</v>
+        <v>0.474382348168073</v>
       </c>
       <c r="N5" t="n">
-        <v>1.054531085219345</v>
+        <v>1.054163177265184</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.32501633913364</v>
+        <v>10.40931022918789</v>
       </c>
       <c r="E6" t="n">
-        <v>426.9508247828504</v>
+        <v>395.0184140477177</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.5129858170352183</v>
+        <v>-0.5081690556003434</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8092161134186174</v>
+        <v>0.809177816977641</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.6339293157028923</v>
+        <v>-0.6280066568043164</v>
       </c>
       <c r="I6" t="n">
         <v>0.5751178664414889</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.6672516296121749</v>
+        <v>0.6672428757678488</v>
       </c>
       <c r="N6" t="n">
-        <v>1.093018051503127</v>
+        <v>1.092965650751113</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.32445983209593</v>
+        <v>10.36925107064565</v>
       </c>
       <c r="E7" t="n">
-        <v>302.3129309458538</v>
+        <v>294.1661936313288</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3434365358788751</v>
+        <v>-0.3410808455547847</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7088345358526849</v>
+        <v>0.7087724960565316</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4845087513487782</v>
+        <v>-0.4812275412103182</v>
       </c>
       <c r="I7" t="n">
         <v>0.4277673545966229</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.7507204192629132</v>
+        <v>0.7506730809725436</v>
       </c>
       <c r="N7" t="n">
-        <v>1.077199807430572</v>
+        <v>1.077051074387685</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.194903905479146</v>
+        <v>9.238504343017246</v>
       </c>
       <c r="E8" t="n">
-        <v>399.5656543554236</v>
+        <v>388.8441662560173</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.376849250689968</v>
+        <v>-0.3750390049509272</v>
       </c>
       <c r="G8" t="n">
-        <v>1.16096630336133</v>
+        <v>1.160927385475131</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3245996456562791</v>
+        <v>-0.32305121719343</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7375563047920947</v>
+        <v>0.7374979512525771</v>
       </c>
       <c r="N8" t="n">
-        <v>1.733356781179268</v>
+        <v>1.733183211962187</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>6.885026153787469</v>
+        <v>6.909625010554283</v>
       </c>
       <c r="E9" t="n">
-        <v>196.5895015239688</v>
+        <v>185.1755540762568</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2957780739218845</v>
+        <v>0.3002343705930313</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4809762640610218</v>
+        <v>0.4810361555384817</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6149535767618647</v>
+        <v>0.6241409655724168</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6740359581205013</v>
+        <v>0.6740574254072543</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6562659620934189</v>
+        <v>0.6563767915351418</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.331060157436462</v>
+        <v>6.340794378201136</v>
       </c>
       <c r="E10" t="n">
-        <v>850.9838353654575</v>
+        <v>724.4511340846424</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8106476416212571</v>
+        <v>0.8142605767666913</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8179347365166608</v>
+        <v>0.8178935574542694</v>
       </c>
       <c r="H10" t="n">
-        <v>0.9910908602238399</v>
+        <v>0.99555812531537</v>
       </c>
       <c r="I10" t="n">
         <v>0.3268819295856837</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.664250696467938</v>
+        <v>0.6641530994060098</v>
       </c>
       <c r="N10" t="n">
-        <v>1.099825640420954</v>
+        <v>1.099622431260522</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.281331062509398</v>
+        <v>6.328275276564609</v>
       </c>
       <c r="E11" t="n">
-        <v>282.5145961306632</v>
+        <v>282.992433502624</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.3206488989780534</v>
+        <v>-0.3138404841561705</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9498169999488338</v>
+        <v>0.9497538547390664</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.3375901873680157</v>
+        <v>-0.3304440225119112</v>
       </c>
       <c r="I11" t="n">
         <v>0.6126386245816655</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.7138309257285782</v>
+        <v>0.7138260781410199</v>
       </c>
       <c r="N11" t="n">
-        <v>1.372487718627198</v>
+        <v>1.372404313296785</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.142129050896719</v>
+        <v>6.089118299057487</v>
       </c>
       <c r="E12" t="n">
-        <v>105.752247033673</v>
+        <v>101.1512943087344</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.3062312606164028</v>
+        <v>-0.3040376640287904</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6527702787867765</v>
+        <v>0.6527402664461478</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4691256182581674</v>
+        <v>-0.4657865917850099</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7894129105632541</v>
+        <v>0.7893882517471966</v>
       </c>
       <c r="N12" t="n">
-        <v>1.043128392812961</v>
+        <v>1.043060892069144</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.439764031229545</v>
+        <v>4.45975863931579</v>
       </c>
       <c r="E13" t="n">
-        <v>279.13691459733</v>
+        <v>268.6612840066236</v>
       </c>
       <c r="F13" t="n">
-        <v>1.477946358817843</v>
+        <v>1.483687022968585</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8573427081506356</v>
+        <v>0.8573277311241463</v>
       </c>
       <c r="H13" t="n">
-        <v>1.723868815547407</v>
+        <v>1.730594927826659</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.6015599930834816</v>
+        <v>0.6015311203981966</v>
       </c>
       <c r="N13" t="n">
-        <v>1.044014603335724</v>
+        <v>1.043959310179818</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.326480718840996</v>
+        <v>4.34268952800438</v>
       </c>
       <c r="E14" t="n">
-        <v>121.3738490206422</v>
+        <v>117.9358755227557</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4356148844874015</v>
+        <v>-0.4338243154329852</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8419510827944597</v>
+        <v>0.8419458741734066</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.5173874033650306</v>
+        <v>-0.5152639008521764</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.7602400277477941</v>
+        <v>0.7602363447534548</v>
       </c>
       <c r="N14" t="n">
-        <v>1.295718803386664</v>
+        <v>1.295720711217642</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>3.909673596693526</v>
+        <v>3.911122496227291</v>
       </c>
       <c r="E15" t="n">
-        <v>254.4551639809041</v>
+        <v>212.4808354240752</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.09923216808568924</v>
+        <v>-0.09857578316623772</v>
       </c>
       <c r="G15" t="n">
-        <v>0.788296434880192</v>
+        <v>0.7882849776536622</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.1258817922990745</v>
+        <v>-0.1250509472597708</v>
       </c>
       <c r="I15" t="n">
         <v>0.4268646717284502</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.7137459704988954</v>
+        <v>0.7136612340606867</v>
       </c>
       <c r="N15" t="n">
-        <v>1.138954569211054</v>
+        <v>1.138817038829664</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3.817484707894844</v>
+        <v>3.867357877192547</v>
       </c>
       <c r="E16" t="n">
-        <v>142.9817512884928</v>
+        <v>144.7946910176822</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3518851327917016</v>
+        <v>0.3723842418976062</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9556314260734823</v>
+        <v>0.9552428226383407</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3682226465045571</v>
+        <v>0.3898320228872241</v>
       </c>
       <c r="I16" t="n">
         <v>0.3858131487889274</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.5151800128695355</v>
+        <v>0.5151962029936729</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9966039361679699</v>
+        <v>0.9962424343915949</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.582969171978111</v>
+        <v>3.581743349909522</v>
       </c>
       <c r="E17" t="n">
-        <v>105.8768899009572</v>
+        <v>103.7788868189046</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1407003154809585</v>
+        <v>-0.142164906447206</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7542012076258751</v>
+        <v>0.7541859429074951</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1865554099599818</v>
+        <v>-0.188501135275924</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7203320273780864</v>
+        <v>0.7204171133822747</v>
       </c>
       <c r="N17" t="n">
-        <v>1.099747839880811</v>
+        <v>1.099869233554148</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.011871129574472</v>
+        <v>3.021165618915236</v>
       </c>
       <c r="E18" t="n">
-        <v>78.71776636331518</v>
+        <v>73.75687272953955</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4826773413257583</v>
+        <v>-0.4819694104014165</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7389022992006277</v>
+        <v>0.7389013811991731</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6532356738474584</v>
+        <v>-0.6522783996143325</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7649891379599251</v>
+        <v>0.764991737794827</v>
       </c>
       <c r="N18" t="n">
-        <v>1.14423560090787</v>
+        <v>1.144252374906439</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.935690891762875</v>
+        <v>2.931658804811403</v>
       </c>
       <c r="E19" t="n">
-        <v>90.56410696350591</v>
+        <v>90.77817090110823</v>
       </c>
       <c r="F19" t="n">
-        <v>0.09746984743237097</v>
+        <v>0.09656566158123625</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4765179177580218</v>
+        <v>0.4765151481589678</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2045460281765662</v>
+        <v>0.2026497204849015</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7157652581710697</v>
+        <v>0.7158032771409352</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6904353508480718</v>
+        <v>0.6904766444470622</v>
       </c>
     </row>
     <row r="20">
@@ -1485,10 +1485,10 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.56416745571162</v>
+        <v>2.564915041980337</v>
       </c>
       <c r="E20" t="n">
-        <v>118.3091051128497</v>
+        <v>114.7271934613945</v>
       </c>
       <c r="F20" t="n">
         <v>-0.3242629489733968</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7321300094934824</v>
+        <v>0.7321185381212801</v>
       </c>
       <c r="N20" t="n">
-        <v>1.142436811065567</v>
+        <v>1.142433194930889</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-08-03.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-08-03.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>568.1851174145963</v>
+        <v>569.5237387020474</v>
       </c>
       <c r="E2" t="n">
-        <v>14207.67797221199</v>
+        <v>12839.36980453675</v>
       </c>
       <c r="F2" t="n">
-        <v>0.600348947410442</v>
+        <v>0.6048945609315572</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4939936888562471</v>
+        <v>0.494001072289192</v>
       </c>
       <c r="H2" t="n">
-        <v>1.215296796200861</v>
+        <v>1.224480258976943</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>221.0860945667272</v>
+        <v>222.5914940774558</v>
       </c>
       <c r="E3" t="n">
-        <v>5112.198452073358</v>
+        <v>4646.478606999302</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2315938276526264</v>
+        <v>0.2427711611308407</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5919167287287056</v>
+        <v>0.5919614676124516</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3912608250657725</v>
+        <v>0.4101131144734904</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8907359084898543</v>
+        <v>0.8907234494350755</v>
       </c>
       <c r="N3" t="n">
-        <v>1.067304091141809</v>
+        <v>1.067353878243694</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>37.05499449884983</v>
+        <v>37.14583176236986</v>
       </c>
       <c r="E4" t="n">
-        <v>551.5576258786034</v>
+        <v>431.5975116919532</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3285390010123694</v>
+        <v>-0.3263273684347475</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5571982329649345</v>
+        <v>0.5572166403566651</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.5896267819518461</v>
+        <v>-0.5856382326017235</v>
       </c>
       <c r="I4" t="n">
         <v>0.3496897913141569</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.7371024041599193</v>
+        <v>0.7371145466906499</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8314117495368041</v>
+        <v>0.8314404852638539</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>35.27363958126086</v>
+        <v>35.54610255666407</v>
       </c>
       <c r="E5" t="n">
-        <v>1394.773667283345</v>
+        <v>1337.927343795626</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6222296365726347</v>
+        <v>0.6382804538175726</v>
       </c>
       <c r="G5" t="n">
-        <v>1.097743115030809</v>
+        <v>1.097549395490297</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5668262711492128</v>
+        <v>0.5815505492875246</v>
       </c>
       <c r="I5" t="n">
         <v>0.3422195892575038</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.474382348168073</v>
+        <v>0.4743662423080042</v>
       </c>
       <c r="N5" t="n">
-        <v>1.054163177265184</v>
+        <v>1.053925612091317</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.40931022918789</v>
+        <v>10.47693023210392</v>
       </c>
       <c r="E6" t="n">
-        <v>395.0184140477177</v>
+        <v>383.1033757475739</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.5081690556003434</v>
+        <v>-0.5050100192659337</v>
       </c>
       <c r="G6" t="n">
-        <v>0.809177816977641</v>
+        <v>0.8092006808472538</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.6280066568043164</v>
+        <v>-0.6240850152735602</v>
       </c>
       <c r="I6" t="n">
         <v>0.5751178664414889</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.6672428757678488</v>
+        <v>0.6672551500433574</v>
       </c>
       <c r="N6" t="n">
-        <v>1.092965650751113</v>
+        <v>1.093000303039493</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.36925107064565</v>
+        <v>10.42543895278368</v>
       </c>
       <c r="E7" t="n">
-        <v>294.1661936313288</v>
+        <v>281.2179490191925</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3410808455547847</v>
+        <v>-0.3369534441198991</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7087724960565316</v>
+        <v>0.7086955543801244</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4812275412103182</v>
+        <v>-0.475455845655223</v>
       </c>
       <c r="I7" t="n">
         <v>0.4277673545966229</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.7506730809725436</v>
+        <v>0.7506943865007134</v>
       </c>
       <c r="N7" t="n">
-        <v>1.077051074387685</v>
+        <v>1.076948622693931</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.238504343017246</v>
+        <v>9.302725878630181</v>
       </c>
       <c r="E8" t="n">
-        <v>388.8441662560173</v>
+        <v>352.3907697030099</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3750390049509272</v>
+        <v>-0.3685115399507631</v>
       </c>
       <c r="G8" t="n">
-        <v>1.160927385475131</v>
+        <v>1.160830671409092</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.32305121719343</v>
+        <v>-0.3174550337332488</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7374979512525771</v>
+        <v>0.7375171997475565</v>
       </c>
       <c r="N8" t="n">
-        <v>1.733183211962187</v>
+        <v>1.733058153480125</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>6.909625010554283</v>
+        <v>6.93175689100267</v>
       </c>
       <c r="E9" t="n">
-        <v>185.1755540762568</v>
+        <v>172.9405012573447</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3002343705930313</v>
+        <v>0.3071489940229566</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4810361555384817</v>
+        <v>0.4811657634985503</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6241409655724168</v>
+        <v>0.6383434095345439</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6740574254072543</v>
+        <v>0.6740336849297445</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6563767915351418</v>
+        <v>0.6565207057751106</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.340794378201136</v>
+        <v>6.363943725925406</v>
       </c>
       <c r="E10" t="n">
-        <v>724.4511340846424</v>
+        <v>582.1489326700423</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8142605767666913</v>
+        <v>0.8187096755056809</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8178935574542694</v>
+        <v>0.8178477010174349</v>
       </c>
       <c r="H10" t="n">
-        <v>0.99555812531537</v>
+        <v>1.00105395477321</v>
       </c>
       <c r="I10" t="n">
         <v>0.3268819295856837</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.6641530994060098</v>
+        <v>0.6640788330162336</v>
       </c>
       <c r="N10" t="n">
-        <v>1.099622431260522</v>
+        <v>1.099421392670022</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.328275276564609</v>
+        <v>6.354861192742027</v>
       </c>
       <c r="E11" t="n">
-        <v>282.992433502624</v>
+        <v>269.2044259191741</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.3138404841561705</v>
+        <v>-0.3107646148543914</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9497538547390664</v>
+        <v>0.9497506219963398</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.3304440225119112</v>
+        <v>-0.3272065399664346</v>
       </c>
       <c r="I11" t="n">
         <v>0.6126386245816655</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.7138260781410199</v>
+        <v>0.7138258916169505</v>
       </c>
       <c r="N11" t="n">
-        <v>1.372404313296785</v>
+        <v>1.372378771201147</v>
       </c>
     </row>
     <row r="12">
@@ -1053,10 +1053,10 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.089118299057487</v>
+        <v>6.100975450773331</v>
       </c>
       <c r="E12" t="n">
-        <v>101.1512943087344</v>
+        <v>97.04964186697501</v>
       </c>
       <c r="F12" t="n">
         <v>-0.3040376640287904</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7893882517471966</v>
+        <v>0.7893316520605951</v>
       </c>
       <c r="N12" t="n">
-        <v>1.043060892069144</v>
+        <v>1.042970515211336</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.45975863931579</v>
+        <v>4.469338513071919</v>
       </c>
       <c r="E13" t="n">
-        <v>268.6612840066236</v>
+        <v>222.0805691629994</v>
       </c>
       <c r="F13" t="n">
-        <v>1.483687022968585</v>
+        <v>1.495178059043696</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8573277311241463</v>
+        <v>0.8573116901983447</v>
       </c>
       <c r="H13" t="n">
-        <v>1.730594927826659</v>
+        <v>1.744030877145484</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.6015311203981966</v>
+        <v>0.6015273629640686</v>
       </c>
       <c r="N13" t="n">
-        <v>1.043959310179818</v>
+        <v>1.043917653566116</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.34268952800438</v>
+        <v>4.369172514088068</v>
       </c>
       <c r="E14" t="n">
-        <v>117.9358755227557</v>
+        <v>111.3542276945528</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4338243154329852</v>
+        <v>-0.4296409509406059</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8419458741734066</v>
+        <v>0.8419681466516166</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.5152639008521764</v>
+        <v>-0.5102817162967801</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.7602363447534548</v>
+        <v>0.760244997862458</v>
       </c>
       <c r="N14" t="n">
-        <v>1.295720711217642</v>
+        <v>1.295750369296153</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>3.911122496227291</v>
+        <v>3.908003631522575</v>
       </c>
       <c r="E15" t="n">
-        <v>212.4808354240752</v>
+        <v>204.9203164870349</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.09857578316623772</v>
+        <v>-0.09956031682054045</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7882849776536622</v>
+        <v>0.7883023471521192</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.1250509472597708</v>
+        <v>-0.1262971208702088</v>
       </c>
       <c r="I15" t="n">
         <v>0.4268646717284502</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.7136612340606867</v>
+        <v>0.7135386280365482</v>
       </c>
       <c r="N15" t="n">
-        <v>1.138817038829664</v>
+        <v>1.138629462196048</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3.867357877192547</v>
+        <v>3.900414731438228</v>
       </c>
       <c r="E16" t="n">
-        <v>144.7946910176822</v>
+        <v>145.0261553514684</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3723842418976062</v>
+        <v>0.3839479580718053</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9552428226383407</v>
+        <v>0.9550982588624096</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3898320228872241</v>
+        <v>0.4019983855159727</v>
       </c>
       <c r="I16" t="n">
         <v>0.3858131487889274</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.5151962029936729</v>
+        <v>0.5151882198003435</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9962424343915949</v>
+        <v>0.9960613434249375</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.581743349909522</v>
+        <v>3.577487012015005</v>
       </c>
       <c r="E17" t="n">
-        <v>103.7788868189046</v>
+        <v>96.05208958862183</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.142164906447206</v>
+        <v>-0.1434459236130037</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7541859429074951</v>
+        <v>0.7541749804542343</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.188501135275924</v>
+        <v>-0.1902024428423855</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7204171133822747</v>
+        <v>0.720453636326288</v>
       </c>
       <c r="N17" t="n">
-        <v>1.099869233554148</v>
+        <v>1.099892566177427</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.021165618915236</v>
+        <v>3.026144512213807</v>
       </c>
       <c r="E18" t="n">
-        <v>73.75687272953955</v>
+        <v>69.81812343595794</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4819694104014165</v>
+        <v>-0.4807890012173421</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7389013811991731</v>
+        <v>0.7389040328186396</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6522783996143325</v>
+        <v>-0.6506785453360078</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.764991737794827</v>
+        <v>0.764992262257574</v>
       </c>
       <c r="N18" t="n">
-        <v>1.144252374906439</v>
+        <v>1.144240163361975</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.931658804811403</v>
+        <v>2.949531053744323</v>
       </c>
       <c r="E19" t="n">
-        <v>90.77817090110823</v>
+        <v>89.48788479029429</v>
       </c>
       <c r="F19" t="n">
-        <v>0.09656566158123625</v>
+        <v>0.1038042311447209</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4765151481589678</v>
+        <v>0.4765672036104967</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2026497204849015</v>
+        <v>0.2178165647117446</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7158032771409352</v>
+        <v>0.7157957415618841</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6904766444470622</v>
+        <v>0.6905344827121184</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.564915041980337</v>
+        <v>2.574803772445593</v>
       </c>
       <c r="E20" t="n">
-        <v>114.7271934613945</v>
+        <v>108.340766943262</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3242629489733968</v>
+        <v>-0.3212875184106445</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7708516570061898</v>
+        <v>0.7708468805691315</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4206554478104897</v>
+        <v>-0.4167981041493371</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7321185381212801</v>
+        <v>0.7321206422037361</v>
       </c>
       <c r="N20" t="n">
-        <v>1.142433194930889</v>
+        <v>1.142412324385892</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-08-03.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-08-03.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>569.5237387020474</v>
+        <v>568.2563089111264</v>
       </c>
       <c r="E2" t="n">
-        <v>12839.36980453675</v>
+        <v>12506.78847972187</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6048945609315572</v>
+        <v>0.6009823064292974</v>
       </c>
       <c r="G2" t="n">
-        <v>0.494001072289192</v>
+        <v>0.4939939852183705</v>
       </c>
       <c r="H2" t="n">
-        <v>1.224480258976943</v>
+        <v>1.21657818599478</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>222.5914940774558</v>
+        <v>221.3972971479443</v>
       </c>
       <c r="E3" t="n">
-        <v>4646.478606999302</v>
+        <v>4582.013458874369</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2427711611308407</v>
+        <v>0.2340008059204042</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5919614676124516</v>
+        <v>0.5919176073795923</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4101131144734904</v>
+        <v>0.3953266518904906</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8907234494350755</v>
+        <v>0.8907368814908553</v>
       </c>
       <c r="N3" t="n">
-        <v>1.067353878243694</v>
+        <v>1.067306201033517</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>37.14583176236986</v>
+        <v>37.01048875535769</v>
       </c>
       <c r="E4" t="n">
-        <v>431.5975116919532</v>
+        <v>421.8039568672639</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3263273684347475</v>
+        <v>-0.329644151931111</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5572166403566651</v>
+        <v>0.5571944837341721</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.5856382326017235</v>
+        <v>-0.5916141698351387</v>
       </c>
       <c r="I4" t="n">
         <v>0.3496897913141569</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.7371145466906499</v>
+        <v>0.737106536156642</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8314404852638539</v>
+        <v>0.8314103170493632</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>35.54610255666407</v>
+        <v>35.52078607478968</v>
       </c>
       <c r="E5" t="n">
-        <v>1337.927343795626</v>
+        <v>1346.557473546401</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6382804538175726</v>
+        <v>0.6389232872771586</v>
       </c>
       <c r="G5" t="n">
-        <v>1.097549395490297</v>
+        <v>1.097542963023485</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5815505492875246</v>
+        <v>0.5821396599519602</v>
       </c>
       <c r="I5" t="n">
         <v>0.3422195892575038</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.4743662423080042</v>
+        <v>0.4744594079888164</v>
       </c>
       <c r="N5" t="n">
-        <v>1.053925612091317</v>
+        <v>1.05414154840007</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.47693023210392</v>
+        <v>10.42011621374651</v>
       </c>
       <c r="E6" t="n">
-        <v>383.1033757475739</v>
+        <v>378.5779704054767</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.5050100192659337</v>
+        <v>-0.507555184906922</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8092006808472538</v>
+        <v>0.8091792926742899</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.6240850152735602</v>
+        <v>-0.6272468777957503</v>
       </c>
       <c r="I6" t="n">
         <v>0.5751178664414889</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.6672551500433574</v>
+        <v>0.6672433603839526</v>
       </c>
       <c r="N6" t="n">
-        <v>1.093000303039493</v>
+        <v>1.092967782104535</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.42543895278368</v>
+        <v>10.34461679127374</v>
       </c>
       <c r="E7" t="n">
-        <v>281.2179490191925</v>
+        <v>288.4691752506062</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3369534441198991</v>
+        <v>-0.3425533931051257</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7086955543801244</v>
+        <v>0.7088097308902229</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.475455845655223</v>
+        <v>-0.4832797550266402</v>
       </c>
       <c r="I7" t="n">
         <v>0.4277673545966229</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.7506943865007134</v>
+        <v>0.7506173403141664</v>
       </c>
       <c r="N7" t="n">
-        <v>1.076948622693931</v>
+        <v>1.077027030510155</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.302725878630181</v>
+        <v>9.239562762235273</v>
       </c>
       <c r="E8" t="n">
-        <v>352.3907697030099</v>
+        <v>350.9410786252953</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3685115399507631</v>
+        <v>-0.3746768022072089</v>
       </c>
       <c r="G8" t="n">
-        <v>1.160830671409092</v>
+        <v>1.160920230683076</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3174550337332488</v>
+        <v>-0.3227412119321514</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7375171997475565</v>
+        <v>0.7374923696508524</v>
       </c>
       <c r="N8" t="n">
-        <v>1.733058153480125</v>
+        <v>1.733158373423525</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>6.93175689100267</v>
+        <v>6.912839538789224</v>
       </c>
       <c r="E9" t="n">
-        <v>172.9405012573447</v>
+        <v>174.2050912982191</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3071489940229566</v>
+        <v>0.3024639170525627</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4811657634985503</v>
+        <v>0.4810730808059331</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6383434095345439</v>
+        <v>0.6287275865568082</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6740336849297445</v>
+        <v>0.6740250778674304</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6565207057751106</v>
+        <v>0.6563952810210966</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.363943725925406</v>
+        <v>6.328757049559471</v>
       </c>
       <c r="E10" t="n">
-        <v>582.1489326700423</v>
+        <v>538.7200180603116</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8187096755056809</v>
+        <v>0.8081474079705229</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8178477010174349</v>
+        <v>0.8179653039501791</v>
       </c>
       <c r="H10" t="n">
-        <v>1.00105395477321</v>
+        <v>0.9879971730680471</v>
       </c>
       <c r="I10" t="n">
         <v>0.3268819295856837</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.6640788330162336</v>
+        <v>0.6640740835499628</v>
       </c>
       <c r="N10" t="n">
-        <v>1.099421392670022</v>
+        <v>1.099587395494834</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.354861192742027</v>
+        <v>6.259496256138759</v>
       </c>
       <c r="E11" t="n">
-        <v>269.2044259191741</v>
+        <v>276.4150435510722</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.3107646148543914</v>
+        <v>-0.3241134733783542</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9497506219963398</v>
+        <v>0.9498788818714219</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.3272065399664346</v>
+        <v>-0.3412155797587539</v>
       </c>
       <c r="I11" t="n">
         <v>0.6126386245816655</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.7138258916169505</v>
+        <v>0.7137132113397917</v>
       </c>
       <c r="N11" t="n">
-        <v>1.372378771201147</v>
+        <v>1.372367128852021</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.100975450773331</v>
+        <v>6.067211407238065</v>
       </c>
       <c r="E12" t="n">
-        <v>97.04964186697501</v>
+        <v>99.70545286596101</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.3040376640287904</v>
+        <v>-0.3091534268553099</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6527402664461478</v>
+        <v>0.6528277664357824</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4657865917850099</v>
+        <v>-0.4735604745232919</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7893316520605951</v>
+        <v>0.7892639995339363</v>
       </c>
       <c r="N12" t="n">
-        <v>1.042970515211336</v>
+        <v>1.043035885783394</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.469338513071919</v>
+        <v>4.446824570190871</v>
       </c>
       <c r="E13" t="n">
-        <v>222.0805691629994</v>
+        <v>216.523307629887</v>
       </c>
       <c r="F13" t="n">
-        <v>1.495178059043696</v>
+        <v>1.480816286003367</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8573116901983447</v>
+        <v>0.8573346399441766</v>
       </c>
       <c r="H13" t="n">
-        <v>1.744030877145484</v>
+        <v>1.727232537926832</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.6015273629640686</v>
+        <v>0.6015201025648362</v>
       </c>
       <c r="N13" t="n">
-        <v>1.043917653566116</v>
+        <v>1.043947975041924</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.369172514088068</v>
+        <v>4.330925844730064</v>
       </c>
       <c r="E14" t="n">
-        <v>111.3542276945528</v>
+        <v>110.8505300661632</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4296409509406059</v>
+        <v>-0.4356148844874015</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8419681466516166</v>
+        <v>0.8419510827944597</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.5102817162967801</v>
+        <v>-0.5173874033650306</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.760244997862458</v>
+        <v>0.7602270565898971</v>
       </c>
       <c r="N14" t="n">
-        <v>1.295750369296153</v>
+        <v>1.295712119212471</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>3.908003631522575</v>
+        <v>3.869420146770697</v>
       </c>
       <c r="E15" t="n">
-        <v>204.9203164870349</v>
+        <v>201.9783595839399</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.09956031682054045</v>
+        <v>-0.1093911962265908</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7883023471521192</v>
+        <v>0.788536633366125</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.1262971208702088</v>
+        <v>-0.1387268410848826</v>
       </c>
       <c r="I15" t="n">
         <v>0.4268646717284502</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.7135386280365482</v>
+        <v>0.7134047828356497</v>
       </c>
       <c r="N15" t="n">
-        <v>1.138629462196048</v>
+        <v>1.138770556965063</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3.900414731438228</v>
+        <v>3.836816773499768</v>
       </c>
       <c r="E16" t="n">
-        <v>145.0261553514684</v>
+        <v>146.267311593945</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3839479580718053</v>
+        <v>0.3570028533466298</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9550982588624096</v>
+        <v>0.9555184907620726</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4019983855159727</v>
+        <v>0.3736221295538746</v>
       </c>
       <c r="I16" t="n">
         <v>0.3858131487889274</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.5151882198003435</v>
+        <v>0.5150185649034434</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9960613434249375</v>
+        <v>0.9961857362158958</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.577487012015005</v>
+        <v>3.536347766355834</v>
       </c>
       <c r="E17" t="n">
-        <v>96.05208958862183</v>
+        <v>91.62091243909579</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1434459236130037</v>
+        <v>-0.155865734256291</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7541749804542343</v>
+        <v>0.7541847878546325</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1902024428423855</v>
+        <v>-0.2066678309697408</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.720453636326288</v>
+        <v>0.7204018783929458</v>
       </c>
       <c r="N17" t="n">
-        <v>1.099892566177427</v>
+        <v>1.099843629848426</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.026144512213807</v>
+        <v>3.012047239845754</v>
       </c>
       <c r="E18" t="n">
-        <v>69.81812343595794</v>
+        <v>70.2821420480939</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4807890012173421</v>
+        <v>-0.4828346272461539</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7389040328186396</v>
+        <v>0.7389027587442727</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6506785453360078</v>
+        <v>-0.6534481317497129</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.764992262257574</v>
+        <v>0.764987501947757</v>
       </c>
       <c r="N18" t="n">
-        <v>1.144240163361975</v>
+        <v>1.144247485815475</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.949531053744323</v>
+        <v>2.943463342742012</v>
       </c>
       <c r="E19" t="n">
-        <v>89.48788479029429</v>
+        <v>89.1116705774768</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1038042311447209</v>
+        <v>0.1019935003569392</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4765672036104967</v>
+        <v>0.4765477833115547</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2178165647117446</v>
+        <v>0.2140257576022728</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7157957415618841</v>
+        <v>0.7157668864804724</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6905344827121184</v>
+        <v>0.6904884134759253</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.574803772445593</v>
+        <v>2.562048554452436</v>
       </c>
       <c r="E20" t="n">
-        <v>108.340766943262</v>
+        <v>106.4167088670168</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3212875184106445</v>
+        <v>-0.3252540503610417</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7708468805691315</v>
+        <v>0.7708573902258619</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4167981041493371</v>
+        <v>-0.421938032228947</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7321206422037361</v>
+        <v>0.7321080898376512</v>
       </c>
       <c r="N20" t="n">
-        <v>1.142412324385892</v>
+        <v>1.142424702288674</v>
       </c>
     </row>
   </sheetData>
